--- a/www/download/IND.labour_force_value.s.mv.zdW13.xlsx
+++ b/www/download/IND.labour_force_value.s.mv.zdW13.xlsx
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Zero depreciation</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -673,7 +678,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Austrália</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -683,84 +688,84 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>6905.976</t>
+          <t>6905975682.68553</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>7192.894</t>
+          <t>7192894488.45646</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>6966.574</t>
+          <t>6966574268.09148</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>7286.386</t>
+          <t>7286386141.88188</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>7817.086</t>
+          <t>7817085931.61751</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>7664.473</t>
+          <t>7664472832.80816</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>7503.404</t>
+          <t>7503404241.46351</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>8019.719</t>
+          <t>8019718592.42711</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>8733.473</t>
+          <t>8733472749.77316</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>10352.511</t>
+          <t>10352511425.3462</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>11183.506</t>
+          <t>11183505643.88</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>11167.442</t>
+          <t>11167441764.8942</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>11695.504</t>
+          <t>11695503682.6154</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>11530.928</t>
+          <t>11530927544.7796</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>11619.069</t>
+          <t>11619068746.1686</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Áustria</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -770,84 +775,84 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>3966.549</t>
+          <t>3966549139.66074</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>3822.621</t>
+          <t>3822620501.64777</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>3290.38</t>
+          <t>3290380242.69567</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>3398.39</t>
+          <t>3398389659.90352</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>3491.637</t>
+          <t>3491636744.86016</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>3379.012</t>
+          <t>3379011654.13916</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3479.331</t>
+          <t>3479331397.72078</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>3484.135</t>
+          <t>3484134969.9835</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>3839.487</t>
+          <t>3839487296.45067</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>4035.969</t>
+          <t>4035968697.91373</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>4110.348</t>
+          <t>4110348321.17164</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>4238.831</t>
+          <t>4238831031.17071</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>4313.031</t>
+          <t>4313031414.23998</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>4542.925</t>
+          <t>4542925237.80753</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>4132.012</t>
+          <t>4132012125.93712</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bélgica</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -857,84 +862,84 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>5041.832</t>
+          <t>5041832495.58354</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>5171.235</t>
+          <t>5171234670.17636</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>5001.634</t>
+          <t>5001633711.3948</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>5066.976</t>
+          <t>5066976461.20708</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>5667.328</t>
+          <t>5667328203.47803</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>6013.843</t>
+          <t>6013843045.83087</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>6499.238</t>
+          <t>6499238072.30633</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>7009.9</t>
+          <t>7009899623.97326</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>8610.635</t>
+          <t>8610635499.64746</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>9149.006</t>
+          <t>9149005829.20912</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>9088.578</t>
+          <t>9088577584.60769</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>9100.422</t>
+          <t>9100422235.47265</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>8808.876</t>
+          <t>8808875999.74884</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>8153.071</t>
+          <t>8153070635.15717</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>8502.035</t>
+          <t>8502035301.22385</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -944,84 +949,84 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1162.224</t>
+          <t>1162223969.77101</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1043.377</t>
+          <t>1043377364.23131</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>883.839</t>
+          <t>883839296.762013</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>1039.555</t>
+          <t>1039554711.89317</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>900.495</t>
+          <t>900495307.596942</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>829.41</t>
+          <t>829410228.931969</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>835.885</t>
+          <t>835884722.328003</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>812.521</t>
+          <t>812521416.687691</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>838.57</t>
+          <t>838569927.049767</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>851.101</t>
+          <t>851100669.330575</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>842.593</t>
+          <t>842592586.500679</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>845.554</t>
+          <t>845553530.985253</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>906.513</t>
+          <t>906513377.633545</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>999.767</t>
+          <t>999766975.424833</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>1066.677</t>
+          <t>1066677377.33329</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1031,84 +1036,84 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>37072.025</t>
+          <t>37072025408.2413</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>36100.721</t>
+          <t>36100721434.4996</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>34689.27</t>
+          <t>34689269820.7934</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>34716.956</t>
+          <t>34716955575.4361</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>32603.17</t>
+          <t>32603169863.9198</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>32446.918</t>
+          <t>32446917788.2256</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>31283.89</t>
+          <t>31283890126.8744</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>31123.195</t>
+          <t>31123194743.4326</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>31107.179</t>
+          <t>31107178880.7214</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>32960.785</t>
+          <t>32960785286.5374</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>35108.499</t>
+          <t>35108498722.3714</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>36466.504</t>
+          <t>36466504185.4077</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>37467.828</t>
+          <t>37467828090.6767</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>39522.625</t>
+          <t>39522625259.0416</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>39313.741</t>
+          <t>39313740788.9262</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Canadá</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1118,84 +1123,84 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>10291.018</t>
+          <t>10291018287.5601</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>9985.127</t>
+          <t>9985126550.68219</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>9472.979</t>
+          <t>9472978614.83326</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>10360.622</t>
+          <t>10360621654.4345</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>11177.327</t>
+          <t>11177327046.029</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>12553.972</t>
+          <t>12553972358.9302</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>13548.641</t>
+          <t>13548640941.3592</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>13796.839</t>
+          <t>13796839491.2018</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>14990.942</t>
+          <t>14990942421.3547</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>15948.54</t>
+          <t>15948539991.3392</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>17355.517</t>
+          <t>17355517276.2366</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>18323.399</t>
+          <t>18323399238.3343</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>17891.356</t>
+          <t>17891355637.3842</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>17948.347</t>
+          <t>17948347455.4281</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>15868.391</t>
+          <t>15868390869.642</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1205,84 +1210,84 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>529371.285</t>
+          <t>529371285481.361</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>526690.805</t>
+          <t>526690805308.109</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>527164.761</t>
+          <t>527164760702.685</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>520172.102</t>
+          <t>520172102125.903</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>505492.465</t>
+          <t>505492465120.717</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>495215.057</t>
+          <t>495215057360.946</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>495322.702</t>
+          <t>495322702050.771</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>497726.653</t>
+          <t>497726652527.186</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>491757.306</t>
+          <t>491757306184.709</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>485733.451</t>
+          <t>485733451241.381</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>473007.591</t>
+          <t>473007590901.797</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>464216.354</t>
+          <t>464216354086.268</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>436425.088</t>
+          <t>436425087782.813</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>452843.739</t>
+          <t>452843739404.218</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>453451.599</t>
+          <t>453451598806.18</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Chipre</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1292,84 +1297,84 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>180.91</t>
+          <t>180909645.797909</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>188.671</t>
+          <t>188670562.074021</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>164.834</t>
+          <t>164833654.668099</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>174.803</t>
+          <t>174803147.167746</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>194.804</t>
+          <t>194804107.043897</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>196.431</t>
+          <t>196431060.815916</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>221.241</t>
+          <t>221240642.870125</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>230.497</t>
+          <t>230497217.972361</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>267.62</t>
+          <t>267620432.865848</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>259.625</t>
+          <t>259625447.166941</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>263.012</t>
+          <t>263011882.658186</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>271.127</t>
+          <t>271126922.779541</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>255.785</t>
+          <t>255785164.290961</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>317.551</t>
+          <t>317551095.543769</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>266.015</t>
+          <t>266014707.820441</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>República Tcheca</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1379,84 +1384,84 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1642.916</t>
+          <t>1642916308.35956</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2322.328</t>
+          <t>2322328484.79243</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2091.605</t>
+          <t>2091604804.50066</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2118.633</t>
+          <t>2118632903.62114</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2065.186</t>
+          <t>2065185859.26022</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>1990.646</t>
+          <t>1990646451.15151</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2072.515</t>
+          <t>2072515160.33446</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2116.364</t>
+          <t>2116363979.26062</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2281.627</t>
+          <t>2281627491.60717</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2512.179</t>
+          <t>2512179195.83279</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2674.18</t>
+          <t>2674179633.89609</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>2630.476</t>
+          <t>2630476481.1758</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>2757.773</t>
+          <t>2757773120.58789</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2923.652</t>
+          <t>2923652050.53211</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2517.702</t>
+          <t>2517701642.9049</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alemanha</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1466,84 +1471,84 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>48292.44</t>
+          <t>48292439560.8063</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>43046.638</t>
+          <t>43046638167.1699</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>37196.779</t>
+          <t>37196778989.9941</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>38704.486</t>
+          <t>38704486031.4942</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>39934.625</t>
+          <t>39934625042.344</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>42390.498</t>
+          <t>42390497869.207</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>41282.205</t>
+          <t>41282205426.3496</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>40559.616</t>
+          <t>40559615980.8762</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>46314.62</t>
+          <t>46314619660.5257</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>47216.657</t>
+          <t>47216657223.1253</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>44736.843</t>
+          <t>44736843031.9826</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>45058.934</t>
+          <t>45058934252.2315</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>46909.023</t>
+          <t>46909022578.1856</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>47269.4</t>
+          <t>47269399580.8871</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>44312.542</t>
+          <t>44312542215.4257</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dinamarca</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1553,84 +1558,84 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>3684.186</t>
+          <t>3684186356.15114</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>3614.367</t>
+          <t>3614366553.13279</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2681.172</t>
+          <t>2681172208.60737</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>3148.726</t>
+          <t>3148726407.91773</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>3251.7</t>
+          <t>3251699743.52911</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>3156.632</t>
+          <t>3156632072.44351</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>3354.857</t>
+          <t>3354856607.00086</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>3453.072</t>
+          <t>3453071543.23834</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>3945.059</t>
+          <t>3945058633.29537</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>3958.631</t>
+          <t>3958630771.90836</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>4004.69</t>
+          <t>4004689910.38665</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>4150.636</t>
+          <t>4150635648.34067</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>4216.071</t>
+          <t>4216071106.48857</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>4193.046</t>
+          <t>4193045982.41786</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>3636.222</t>
+          <t>3636222311.12278</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Espanha</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1640,84 +1645,84 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>10596.713</t>
+          <t>10596713157.5754</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>10324.671</t>
+          <t>10324671207.7185</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>9152.847</t>
+          <t>9152847488.22905</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>10498</t>
+          <t>10497999661.6537</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>11707.019</t>
+          <t>11707018996.0614</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>12213.457</t>
+          <t>12213457477.335</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>13419.208</t>
+          <t>13419207657.2807</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>14401.11</t>
+          <t>14401110288.5614</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>16404.706</t>
+          <t>16404705695.2039</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>17559.642</t>
+          <t>17559642366.0352</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>18371.804</t>
+          <t>18371804441.6297</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>19452.825</t>
+          <t>19452824897.0256</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>19731.602</t>
+          <t>19731602412.57</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>20081.45</t>
+          <t>20081449993.2322</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>17020.697</t>
+          <t>17020696649.342</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Estônia</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1727,84 +1732,84 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>250.748</t>
+          <t>250748040.740642</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>266.24</t>
+          <t>266240201.517871</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>273.333</t>
+          <t>273332980.293173</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>284.261</t>
+          <t>284260925.265428</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>262.391</t>
+          <t>262390881.171149</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>299.046</t>
+          <t>299045720.699941</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>306.871</t>
+          <t>306870801.759823</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>388.637</t>
+          <t>388637439.639801</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>463.16</t>
+          <t>463160225.07552</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>474.622</t>
+          <t>474622029.645861</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>461.364</t>
+          <t>461363743.533385</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>475.758</t>
+          <t>475758344.19144</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>496.177</t>
+          <t>496176675.796268</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>549.104</t>
+          <t>549103982.523397</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>439.279</t>
+          <t>439279205.991685</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Finlândia</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1814,84 +1819,84 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>1895.656</t>
+          <t>1895655766.94448</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2001.292</t>
+          <t>2001291554.95239</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1737.915</t>
+          <t>1737914621.84588</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>1902.111</t>
+          <t>1902111164.85676</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>1967.538</t>
+          <t>1967537511.98566</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1816.092</t>
+          <t>1816091514.77935</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1888.237</t>
+          <t>1888237294.1341</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1934.876</t>
+          <t>1934876166.6063</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2155.254</t>
+          <t>2155253975.54752</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2282.801</t>
+          <t>2282801235.89851</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2361.859</t>
+          <t>2361859381.56452</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>2478.05</t>
+          <t>2478050249.03441</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>2542.207</t>
+          <t>2542207018.73518</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2682.804</t>
+          <t>2682804364.40691</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2413.832</t>
+          <t>2413831618.14163</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>França</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1901,84 +1906,84 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>22568.894</t>
+          <t>22568894290.6512</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>22669.093</t>
+          <t>22669093118.1117</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>19561.482</t>
+          <t>19561482189.3724</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>22087.489</t>
+          <t>22087488893.1115</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>24122.758</t>
+          <t>24122757960.0117</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>24514.831</t>
+          <t>24514831121.1862</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>26364.579</t>
+          <t>26364579420.7727</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>27249.36</t>
+          <t>27249360122.4804</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>29747.87</t>
+          <t>29747870300.3185</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>30908.955</t>
+          <t>30908954804.4491</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>31181.91</t>
+          <t>31181910370.1706</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>30545.698</t>
+          <t>30545697662.5641</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>30790.109</t>
+          <t>30790109491.1818</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>31569.625</t>
+          <t>31569624529.5941</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>28917.69</t>
+          <t>28917689845.7175</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Reino Unido</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1988,84 +1993,84 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>21989.279</t>
+          <t>21989278764.9244</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>22485.626</t>
+          <t>22485625620.6839</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>21287.096</t>
+          <t>21287096179.94</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>23525.552</t>
+          <t>23525552470.2349</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>25238.691</t>
+          <t>25238690999.4347</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>26814.98</t>
+          <t>26814979609.8355</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>28619.933</t>
+          <t>28619933088.228</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>29439.294</t>
+          <t>29439294164.6068</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>31408.466</t>
+          <t>31408466013.6511</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>33649.116</t>
+          <t>33649115615.1448</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>33964.227</t>
+          <t>33964226815.1339</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>34429.273</t>
+          <t>34429272840.1635</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>33703.348</t>
+          <t>33703347850.9605</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>30855.445</t>
+          <t>30855444803.6717</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>27823.9</t>
+          <t>27823900244.088</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Grécia</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2075,84 +2080,84 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1878.261</t>
+          <t>1878260809.12526</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1938.013</t>
+          <t>1938012682.35154</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1843.417</t>
+          <t>1843417346.38732</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>1898.66</t>
+          <t>1898659710.75783</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2063.689</t>
+          <t>2063688918.77128</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2190.43</t>
+          <t>2190430074.55858</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2133.837</t>
+          <t>2133837097.2654</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2514.472</t>
+          <t>2514471850.51374</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2598.239</t>
+          <t>2598238993.77558</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2675.631</t>
+          <t>2675631205.7516</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2624.155</t>
+          <t>2624154516.08323</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>2840.824</t>
+          <t>2840823575.8773</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>3030.557</t>
+          <t>3030556887.75171</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>3102.757</t>
+          <t>3102756523.66557</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>2989.264</t>
+          <t>2989264024.34361</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Hungria</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2162,84 +2167,84 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2137.256</t>
+          <t>2137256177.32153</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2053.851</t>
+          <t>2053851380.46595</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1964.411</t>
+          <t>1964410749.22239</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>1987.08</t>
+          <t>1987079871.38388</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2062.51</t>
+          <t>2062510071.46508</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2071.984</t>
+          <t>2071984330.32073</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2038.161</t>
+          <t>2038161457.83902</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2216.99</t>
+          <t>2216990028.08448</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2393.027</t>
+          <t>2393027428.89707</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2071.244</t>
+          <t>2071244040.7654</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2059.043</t>
+          <t>2059043139.20313</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>1987.8</t>
+          <t>1987799817.1198</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>2059.879</t>
+          <t>2059878657.2858</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>2056.027</t>
+          <t>2056027499.40673</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>1848.918</t>
+          <t>1848917810.55899</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Indonésia</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2249,84 +2254,84 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>24589.167</t>
+          <t>24589166968.5266</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>24887.607</t>
+          <t>24887607290.8091</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>22385.292</t>
+          <t>22385291717.3187</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>21368.27</t>
+          <t>21368269531.1748</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>23580.11</t>
+          <t>23580110247.7567</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>25235.933</t>
+          <t>25235933111.0069</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>26363.969</t>
+          <t>26363968863.3367</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>27621.989</t>
+          <t>27621989270.5287</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>29721.081</t>
+          <t>29721081257.7505</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>30303.036</t>
+          <t>30303036197.4741</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>28821.315</t>
+          <t>28821315061.4713</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>28741.681</t>
+          <t>28741680896.15</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>30795.384</t>
+          <t>30795384415.2816</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>30600.011</t>
+          <t>30600010715.6048</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>32788.733</t>
+          <t>32788732662.7409</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Índia</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2336,84 +2341,84 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>275058.506</t>
+          <t>275058505948.462</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>258355.963</t>
+          <t>258355963033.266</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>273954.576</t>
+          <t>273954575622.978</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>272819.283</t>
+          <t>272819282589.765</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>265575.421</t>
+          <t>265575421256.318</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>268872.368</t>
+          <t>268872368481.138</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>277069.892</t>
+          <t>277069891678.349</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>265418.724</t>
+          <t>265418723670.886</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>288034.423</t>
+          <t>288034422990.627</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>303074.689</t>
+          <t>303074688874.18</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>315453.648</t>
+          <t>315453647926.747</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>320190.533</t>
+          <t>320190533160.068</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>302179.324</t>
+          <t>302179323623.303</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>295111.565</t>
+          <t>295111564533.683</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>309631.249</t>
+          <t>309631249072.438</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Irlanda</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2423,84 +2428,84 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>1075.03</t>
+          <t>1075030245.91845</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1155.985</t>
+          <t>1155985056.33811</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1051.693</t>
+          <t>1051692976.84361</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>1090.981</t>
+          <t>1090981251.98834</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>1155.77</t>
+          <t>1155770257.54953</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>1236.501</t>
+          <t>1236501197.0028</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1432.016</t>
+          <t>1432015722.77983</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>1543.485</t>
+          <t>1543485231.92638</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>1413.389</t>
+          <t>1413388935.84473</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>1373.464</t>
+          <t>1373463991.18749</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>1618.901</t>
+          <t>1618900975.68395</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>1687.378</t>
+          <t>1687377692.73051</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>1861.437</t>
+          <t>1861436951.35733</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>1987.452</t>
+          <t>1987452358.01161</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>1975.401</t>
+          <t>1975400724.46839</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Itália</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2510,84 +2515,84 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>15364.839</t>
+          <t>15364839348.6752</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>15143.359</t>
+          <t>15143358672.6266</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>13897.435</t>
+          <t>13897434823.7065</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>14174.071</t>
+          <t>14174070753.8437</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>14506.003</t>
+          <t>14506002829.9653</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>14845.857</t>
+          <t>14845857317.4417</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>15889.49</t>
+          <t>15889489850.9463</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>16620.78</t>
+          <t>16620779767.0552</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>18602.64</t>
+          <t>18602639876.0336</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>20016.258</t>
+          <t>20016257678.6402</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>20365.111</t>
+          <t>20365111034.7442</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>21173.894</t>
+          <t>21173894333.7873</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>20480.657</t>
+          <t>20480656510.2852</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>20792.174</t>
+          <t>20792173855.7271</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>18307.84</t>
+          <t>18307840090.8573</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Japão</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2597,84 +2602,84 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>72910.162</t>
+          <t>72910162344.1449</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>64860.762</t>
+          <t>64860762019.254</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>57654.674</t>
+          <t>57654674160.1096</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>55035.136</t>
+          <t>55035135938.279</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>57171.473</t>
+          <t>57171473295.9255</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>61173.461</t>
+          <t>61173460801.959</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>60097.502</t>
+          <t>60097501609.8496</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>56348.632</t>
+          <t>56348632049.7427</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>58098.884</t>
+          <t>58098884444.4017</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>61693.321</t>
+          <t>61693321043.9636</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>61293.427</t>
+          <t>61293427089.9245</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>59753.981</t>
+          <t>59753980736.2129</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>54204.802</t>
+          <t>54204802319.3255</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>51362.746</t>
+          <t>51362745888.4795</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>48930.593</t>
+          <t>48930592989.5693</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Coreia do Sul</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2684,84 +2689,84 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>17775.783</t>
+          <t>17775782815.2508</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>17219.725</t>
+          <t>17219724816.3372</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>15688.446</t>
+          <t>15688445524.686</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>13292.266</t>
+          <t>13292266010.5517</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>13444.358</t>
+          <t>13444357558.1376</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>14510.452</t>
+          <t>14510451653.8877</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>14806.809</t>
+          <t>14806809448.7076</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>15534.342</t>
+          <t>15534341554.4161</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>16946.422</t>
+          <t>16946422174.2914</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>18141.334</t>
+          <t>18141333586.8977</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>18174.079</t>
+          <t>18174078696.7651</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>19073.742</t>
+          <t>19073742388.3446</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>18587.156</t>
+          <t>18587156208.7465</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>17257.19</t>
+          <t>17257190243.4055</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>16245.441</t>
+          <t>16245441184.6373</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Lituânia</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2771,84 +2776,84 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>557.782</t>
+          <t>557782210.864289</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>567.179</t>
+          <t>567178594.45442</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>558.32</t>
+          <t>558319827.667075</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>689.433</t>
+          <t>689433446.125028</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>695.117</t>
+          <t>695116687.694561</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>721.241</t>
+          <t>721241290.640308</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>680.166</t>
+          <t>680165990.535796</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>714.811</t>
+          <t>714810956.595207</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>807.486</t>
+          <t>807486328.883768</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>714.756</t>
+          <t>714756054.651508</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>779.978</t>
+          <t>779978485.951183</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>826.143</t>
+          <t>826143349.90051</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>830.691</t>
+          <t>830691008.580721</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>929.7</t>
+          <t>929700249.203293</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>813.599</t>
+          <t>813598869.140455</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Luxemburgo</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2858,84 +2863,84 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>255.2</t>
+          <t>255199833.841368</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>224.646</t>
+          <t>224646224.612469</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>193.377</t>
+          <t>193377071.931417</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>199.063</t>
+          <t>199063418.936084</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>220.753</t>
+          <t>220752963.903562</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>240.495</t>
+          <t>240495297.463101</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>229.554</t>
+          <t>229554430.350381</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>253.95</t>
+          <t>253950275.826232</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>271.408</t>
+          <t>271407669.532803</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>287.872</t>
+          <t>287872344.705319</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>310.821</t>
+          <t>310820888.026443</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>312.067</t>
+          <t>312066843.076697</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>284.9</t>
+          <t>284899603.683619</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>347.571</t>
+          <t>347570823.799867</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>302.362</t>
+          <t>302362311.405377</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Letônia</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2945,84 +2950,84 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>324.761</t>
+          <t>324761418.646752</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>347.829</t>
+          <t>347829438.333842</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>341.996</t>
+          <t>341996467.86411</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>361.372</t>
+          <t>361372495.528154</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>355.282</t>
+          <t>355282065.205698</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>310.03</t>
+          <t>310029781.959894</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>300.717</t>
+          <t>300716713.382632</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>294.529</t>
+          <t>294528800.076721</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>317.642</t>
+          <t>317641710.608698</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>320.363</t>
+          <t>320363008.003678</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>347.879</t>
+          <t>347878617.953231</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>390.408</t>
+          <t>390408487.788383</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>462.55</t>
+          <t>462550074.79338</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>521.184</t>
+          <t>521183584.599528</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>384.479</t>
+          <t>384479304.440216</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3032,84 +3037,84 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>9970.753</t>
+          <t>9970753152.19047</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>9804.664</t>
+          <t>9804664262.33217</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>9615.371</t>
+          <t>9615370653.39066</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>10513.137</t>
+          <t>10513137377.5229</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>11484.548</t>
+          <t>11484548347.9781</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>12212.595</t>
+          <t>12212595286.0583</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>13757.31</t>
+          <t>13757310379.1835</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>13913.798</t>
+          <t>13913797980.6068</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>14194.757</t>
+          <t>14194756901.1036</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>14256.344</t>
+          <t>14256343631.0374</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>14076.596</t>
+          <t>14076596494.0186</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>13757.59</t>
+          <t>13757590369.3731</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>13509.488</t>
+          <t>13509487742.9943</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>14142.21</t>
+          <t>14142210278.6616</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>13767.745</t>
+          <t>13767745348.0008</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3119,84 +3124,84 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>87.415</t>
+          <t>87414802.8009134</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>93.781</t>
+          <t>93780819.3089756</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>76.181</t>
+          <t>76181003.8911903</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>83.247</t>
+          <t>83247202.5040526</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>94.605</t>
+          <t>94605160.0480032</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>101.831</t>
+          <t>101831083.699319</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>117.232</t>
+          <t>117231711.140144</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>125.469</t>
+          <t>125469479.531514</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>139.309</t>
+          <t>139308821.544668</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>108.274</t>
+          <t>108273592.978233</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>109.398</t>
+          <t>109397833.860717</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>107.037</t>
+          <t>107036629.132206</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>117.716</t>
+          <t>117715909.978199</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>135.701</t>
+          <t>135700631.523666</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>117.116</t>
+          <t>117115616.318116</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Países Baixos</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3206,84 +3211,84 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>10651.923</t>
+          <t>10651923032.5477</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>10324.478</t>
+          <t>10324478089.5758</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>7125.509</t>
+          <t>7125509346.90427</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>9010.272</t>
+          <t>9010272226.51336</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>9826.181</t>
+          <t>9826181027.26621</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>9524.746</t>
+          <t>9524745923.09501</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>10810.767</t>
+          <t>10810766721.816</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>12099.807</t>
+          <t>12099807162.0328</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>11818.49</t>
+          <t>11818489715.8619</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>11476.529</t>
+          <t>11476528779.2115</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>11123.524</t>
+          <t>11123524215.8505</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>11371.608</t>
+          <t>11371607896.2685</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>11589.637</t>
+          <t>11589637136.6886</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>12754.957</t>
+          <t>12754956594.7117</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>12129.308</t>
+          <t>12129307647.481</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Polônia</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3293,84 +3298,84 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>7827.926</t>
+          <t>7827925540.99053</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>8242.83</t>
+          <t>8242829546.90663</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>8416.875</t>
+          <t>8416874539.72044</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>8726.422</t>
+          <t>8726422346.873</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>8295.953</t>
+          <t>8295952945.68913</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>8115.813</t>
+          <t>8115813376.17699</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>6738.154</t>
+          <t>6738153619.07554</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>6336.036</t>
+          <t>6336035534.12094</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>6074.337</t>
+          <t>6074336560.55771</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>5847.744</t>
+          <t>5847743643.29422</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>6182.794</t>
+          <t>6182793606.96699</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>6311.819</t>
+          <t>6311819140.72499</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>6578.158</t>
+          <t>6578158230.48264</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>7504.166</t>
+          <t>7504165545.87886</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>6726.078</t>
+          <t>6726077964.00959</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3380,84 +3385,84 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>3144.829</t>
+          <t>3144829445.82799</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>3199.043</t>
+          <t>3199042859.81825</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2764.175</t>
+          <t>2764174797.19214</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>3082.13</t>
+          <t>3082129868.7247</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>3118.804</t>
+          <t>3118804265.08536</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>3235.71</t>
+          <t>3235709578.75628</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>3415.681</t>
+          <t>3415680637.4073</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>3398.756</t>
+          <t>3398755803.068</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>3444.319</t>
+          <t>3444318572.45916</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>3462.785</t>
+          <t>3462785041.81296</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>3423.892</t>
+          <t>3423891767.0014</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>3280.582</t>
+          <t>3280582318.5875</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>3284.333</t>
+          <t>3284332777.98118</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>3460.618</t>
+          <t>3460618001.56691</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>3005.542</t>
+          <t>3005541563.86163</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Romênia</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3467,84 +3472,84 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>4136.818</t>
+          <t>4136817853.90314</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>4130.876</t>
+          <t>4130875542.40234</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>3438.068</t>
+          <t>3438068233.18939</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>4122.595</t>
+          <t>4122594515.73763</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>4864.622</t>
+          <t>4864622455.9985</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>5664.966</t>
+          <t>5664966264.23611</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>5837.544</t>
+          <t>5837543521.66786</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>4518.544</t>
+          <t>4518544496.17928</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>4506.545</t>
+          <t>4506544636.7583</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>4032.342</t>
+          <t>4032342072.63431</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>4488.819</t>
+          <t>4488819497.41057</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>4407.722</t>
+          <t>4407722005.31813</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>4664.049</t>
+          <t>4664049474.53373</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>5094.646</t>
+          <t>5094646327.6595</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>4570.511</t>
+          <t>4570510512.25376</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Rússia</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3554,84 +3559,84 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>53107.677</t>
+          <t>53107676776.3632</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>54920.913</t>
+          <t>54920913188.9212</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>49702.806</t>
+          <t>49702805714.7625</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>44731.718</t>
+          <t>44731717852.4648</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>42955.455</t>
+          <t>42955455070.3951</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>48243.961</t>
+          <t>48243960895.7465</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>46917.548</t>
+          <t>46917548194.5728</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>48390.121</t>
+          <t>48390121075.1564</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>52617.717</t>
+          <t>52617716740.1595</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>55268.362</t>
+          <t>55268361833.7373</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>58015.526</t>
+          <t>58015526465.6138</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>58158.621</t>
+          <t>58158621265.7718</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>64979.562</t>
+          <t>64979562186.1261</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>70010.772</t>
+          <t>70010771638.9987</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>68951.058</t>
+          <t>68951058244.7778</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Eslováquia</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3641,84 +3646,84 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>621.876</t>
+          <t>621876210.910831</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>656.089</t>
+          <t>656088918.432608</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>628.465</t>
+          <t>628464935.957282</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>620.512</t>
+          <t>620512398.303574</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>563.314</t>
+          <t>563314184.940113</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>573.016</t>
+          <t>573016468.410269</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>581.493</t>
+          <t>581493183.502706</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>575.205</t>
+          <t>575204834.264591</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>644.406</t>
+          <t>644405829.854967</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>789.012</t>
+          <t>789011599.945575</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>799.11</t>
+          <t>799110476.408873</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>867.122</t>
+          <t>867122388.016242</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>1053.226</t>
+          <t>1053225978.95286</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>1052.239</t>
+          <t>1052239253.85867</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>1196.535</t>
+          <t>1196535103.16199</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Eslovênia</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3728,84 +3733,84 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>778.111</t>
+          <t>778111309.925446</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>744.795</t>
+          <t>744795382.147985</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>643.884</t>
+          <t>643883822.467034</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>679.046</t>
+          <t>679045891.402273</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>688.263</t>
+          <t>688263280.433403</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>704.051</t>
+          <t>704050531.203129</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>735.908</t>
+          <t>735908036.686006</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>748.954</t>
+          <t>748953778.0551</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>838.85</t>
+          <t>838849930.33722</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>796.685</t>
+          <t>796684703.672169</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>765.782</t>
+          <t>765782199.185973</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>772.293</t>
+          <t>772292635.986929</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>777.764</t>
+          <t>777763535.253551</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>1115.923</t>
+          <t>1115923153.59134</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>1075.699</t>
+          <t>1075698696.91584</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Suécia</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3815,84 +3820,84 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>4244.68</t>
+          <t>4244679590.99994</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>4331.869</t>
+          <t>4331869070.42652</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>3672.017</t>
+          <t>3672016648.7754</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>4037.601</t>
+          <t>4037600808.67781</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>4153.527</t>
+          <t>4153526945.03676</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>4612.898</t>
+          <t>4612898320.16499</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>4727.621</t>
+          <t>4727620692.88732</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>4861.165</t>
+          <t>4861165414.26395</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>5197.853</t>
+          <t>5197853079.27416</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>5397.458</t>
+          <t>5397457589.95733</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>5564.304</t>
+          <t>5564303725.12457</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>5633.214</t>
+          <t>5633214182.87314</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>6000.704</t>
+          <t>6000703567.32437</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>5716.087</t>
+          <t>5716087450.23316</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>4874.448</t>
+          <t>4874447963.28599</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Turquia</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3902,84 +3907,84 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>7091.792</t>
+          <t>7091792080.70034</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>8155.875</t>
+          <t>8155874691.12296</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>8489.443</t>
+          <t>8489443194.63235</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>8291.576</t>
+          <t>8291576299.32688</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>8799.81</t>
+          <t>8799809857.92147</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>7862.174</t>
+          <t>7862174326.93954</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>7167.002</t>
+          <t>7167002016.45706</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>6509.191</t>
+          <t>6509190603.08937</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>6781.702</t>
+          <t>6781701753.53577</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>7234.213</t>
+          <t>7234213374.88723</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>7131.565</t>
+          <t>7131565282.6364</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>6791.71</t>
+          <t>6791710045.22589</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>6778.919</t>
+          <t>6778918574.37708</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>12174.155</t>
+          <t>12174155096.8045</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>10710.545</t>
+          <t>10710545468.4118</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>China: Taiwan</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3989,84 +3994,84 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>8162.05</t>
+          <t>8162049621.39148</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>8699.535</t>
+          <t>8699535197.28724</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>7846.87</t>
+          <t>7846869881.02203</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>7508.24</t>
+          <t>7508239862.75788</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>7367.337</t>
+          <t>7367336837.98578</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>7920.404</t>
+          <t>7920404403.58283</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>7703.589</t>
+          <t>7703589172.72522</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>7591.234</t>
+          <t>7591234444.67355</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>7815.72</t>
+          <t>7815719506.09705</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>8025.938</t>
+          <t>8025937928.50414</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>8098.053</t>
+          <t>8098052990.03895</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>8000.612</t>
+          <t>8000611806.18742</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>7349.052</t>
+          <t>7349051862.15474</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>7524.057</t>
+          <t>7524056777.98002</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>6563.821</t>
+          <t>6563821108.14852</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4076,84 +4081,84 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>110764.452</t>
+          <t>110764452076.125</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>110694.112</t>
+          <t>110694112241.97</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>113935.57</t>
+          <t>113935569616.697</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>124001.139</t>
+          <t>124001139415.257</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>130653.363</t>
+          <t>130653363066.927</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>147757.403</t>
+          <t>147757403010.848</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>152799.825</t>
+          <t>152799824783.426</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>155490.948</t>
+          <t>155490947837.918</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>160661.491</t>
+          <t>160661490886.553</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>166394.736</t>
+          <t>166394735872.046</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>169565.466</t>
+          <t>169565465993.496</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>168684.708</t>
+          <t>168684708427.101</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>157995.695</t>
+          <t>157995694636.356</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>147972.185</t>
+          <t>147972184874.24</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>137960.962</t>
+          <t>137960962156.08</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Resto do mundo</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4163,84 +4168,84 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>689507.836</t>
+          <t>689507835948.644</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>686651.773</t>
+          <t>686651772655.516</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>704610.494</t>
+          <t>704610494143.487</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>711330.794</t>
+          <t>711330793805.077</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>738082.053</t>
+          <t>738082053073.131</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>785794.356</t>
+          <t>785794355894.522</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>810353.26</t>
+          <t>810353259521.882</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>812769.769</t>
+          <t>812769769240.058</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>827798.036</t>
+          <t>827798036124.983</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>825469.702</t>
+          <t>825469701695.088</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>854710.248</t>
+          <t>854710247981.291</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>886644.892</t>
+          <t>886644891817.58</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>864274.694</t>
+          <t>864274693872.998</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>895264.434</t>
+          <t>895264433509.561</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>893184.792</t>
+          <t>893184792087.304</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Mundo</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4250,84 +4255,84 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2026937.538</t>
+          <t>2026937537920.91</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1994331.257</t>
+          <t>1994331257462.97</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>1992115.863</t>
+          <t>1992115862595.51</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2004139.093</t>
+          <t>2004139092825.46</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2027672.542</t>
+          <t>2027672541990.59</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2105227.977</t>
+          <t>2105227976868.08</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>2148707.783</t>
+          <t>2148707782707.33</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>2148157.489</t>
+          <t>2148157489406.8</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>2214604.146</t>
+          <t>2214604146257.52</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>2247085.681</t>
+          <t>2247085681215.29</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2284619.955</t>
+          <t>2284619955208.98</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>2315619.266</t>
+          <t>2315619265579.24</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>2242640.623</t>
+          <t>2242640623150.5</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>2283974.004</t>
+          <t>2283974004305.52</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>2260353.441</t>
+          <t>2260353440980.58</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Croácia</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4339,7 +4344,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Suíça</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4351,7 +4356,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4363,7 +4368,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Africa do Sul</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4375,7 +4380,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Resto do mundo - Asia</t>
+          <t>47</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4387,7 +4392,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Resto do mundo - America</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4399,7 +4404,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Resto do mundo - Europa</t>
+          <t>48</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4411,7 +4416,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Resto do mundo - Africa</t>
+          <t>49</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4423,7 +4428,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Resto do mundo - Oriente Medio</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4470,6 +4475,11 @@
           <t>labour_force_value.s.mv</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4504,6 +4514,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Zero depreciation</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>zdW13</t>
